--- a/artfynd/A 18371-2025 artfynd.xlsx
+++ b/artfynd/A 18371-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>67921342</v>
       </c>
       <c r="B2" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566662.8069520034</v>
+        <v>566663</v>
       </c>
       <c r="R2" t="n">
-        <v>6592730.236788827</v>
+        <v>6592730</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2017-09-12</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2017-09-12</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,12 +775,7 @@
         <v>67921343</v>
       </c>
       <c r="B3" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566688.9350361688</v>
+        <v>566689</v>
       </c>
       <c r="R3" t="n">
-        <v>6592750.014689164</v>
+        <v>6592750</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -860,19 +840,9 @@
           <t>2017-09-12</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2017-09-12</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
